--- a/Tools/Config/Datas/__enums__.xlsx
+++ b/Tools/Config/Datas/__enums__.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -1796,15 +1796,15 @@
       </c>
     </row>
     <row r="43">
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="0" t="inlineStr">
         <is>
           <t>AddShield</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="0" t="inlineStr">
         <is>
           <t>//护盾吸收层（挂在 Vital，卸 Buff 掉剩余盾）</t>
         </is>
@@ -1881,7 +1881,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="B49" s="0" t="inlineStr">
         <is>
@@ -1953,7 +1952,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="B54" s="0" t="inlineStr">
         <is>
@@ -2306,7 +2304,6 @@
         </is>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="B77" s="0" t="inlineStr">
         <is>
@@ -2390,6 +2387,47 @@
       <c r="K81" s="0" t="inlineStr">
         <is>
           <t>真实</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t>HitReactionType</t>
+        </is>
+      </c>
+      <c r="C83" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D83" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" s="0" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="J83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="0" t="inlineStr">
+        <is>
+          <t>轻受击：扣血/闪白/顿帧，不断招</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="H84" s="0" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="J84" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="0" t="inlineStr">
+        <is>
+          <t>重受击：短硬直并断招</t>
         </is>
       </c>
     </row>
